--- a/latest/BoM/Positional/pedalboard-display-bom.xlsx
+++ b/latest/BoM/Positional/pedalboard-display-bom.xlsx
@@ -352,7 +352,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.7+1</t>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -985,7 +985,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="59.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="60.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="51.7109375" customWidth="1"/>
@@ -1591,7 +1591,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="51.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
